--- a/Documents/Client-Files/Client BOM/BOM-InterfaceBoard (1).xlsx
+++ b/Documents/Client-Files/Client BOM/BOM-InterfaceBoard (1).xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24718"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ChrisitanRaun-AnnanasMotor\Documents\Client-Files\Client BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XPENDER\Documents\GitHub\ChristianRaun-EthercatDesign\Documents\Client-Files\Client BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16DA309-C145-4C1F-A9DF-27B08E55F7D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="14010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="232">
   <si>
     <t>Bill of Material (BOM)</t>
   </si>
@@ -271,23 +270,7 @@
 Sorry no manufacturer part number, just description..</t>
   </si>
   <si>
-    <t xml:space="preserve">10V 22uF ±10% CASE-A_3216 Tantalum Capacitors ROHS
-</t>
-  </si>
-  <si>
     <t>C2</t>
-  </si>
-  <si>
-    <t>Cap Case-A</t>
-  </si>
-  <si>
-    <t>CA45A-A-10V-22uF-K</t>
-  </si>
-  <si>
-    <t>CEC</t>
-  </si>
-  <si>
-    <t>C141745</t>
   </si>
   <si>
     <t>22uF</t>
@@ -833,20 +816,84 @@
   <si>
     <t>Please change number of pins to 1*6P, the other specifications remain same</t>
   </si>
+  <si>
+    <t>GRM188R61E106MA73J</t>
+  </si>
+  <si>
+    <t>CAP CER 22UF 25V X5R 0805</t>
+  </si>
+  <si>
+    <t>CAP CER 10UF 25V X5R 0603</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>CC0805MKX5R8BB226</t>
+  </si>
+  <si>
+    <t>C784585</t>
+  </si>
+  <si>
+    <t>IND SMD 1.5A 2.2uH ±20% 135mΩ</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>MCS20FC-2R2MMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> R2</t>
+  </si>
+  <si>
+    <t>CRGH0603J100K</t>
+  </si>
+  <si>
+    <t>C2074142</t>
+  </si>
+  <si>
+    <t>RES SMD 100K OHM 5% 1/5W 0603</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                </t>
+  </si>
+  <si>
+    <t>PSA(Prosperity Dielectrics)</t>
+  </si>
+  <si>
+    <t>C375949</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.2uH</t>
+  </si>
+  <si>
+    <t>33uH</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -967,6 +1014,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1006,7 +1066,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1276,25 +1336,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1306,7 +1405,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1315,120 +1414,117 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1455,13 +1551,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1473,10 +1569,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1485,10 +1581,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1497,12 +1593,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1515,53 +1605,123 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1837,60 +1997,60 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD44"/>
-  <sheetFormatPr defaultColWidth="34.44140625" defaultRowHeight="51" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AD47"/>
+  <sheetFormatPr defaultColWidth="34.42578125" defaultRowHeight="51" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.6640625" customWidth="1"/>
-    <col min="3" max="3" width="30.77734375" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" customWidth="1"/>
-    <col min="6" max="6" width="21.77734375" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="11.77734375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="37.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" customWidth="1"/>
-    <col min="13" max="13" width="12.88671875" customWidth="1"/>
-    <col min="14" max="14" width="131.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="34.44140625" customWidth="1"/>
+    <col min="12" max="12" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" customWidth="1"/>
+    <col min="14" max="14" width="131.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="51" customHeight="1" thickBot="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="51"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="50"/>
     </row>
     <row r="2" spans="1:30" ht="51" customHeight="1" thickBot="1">
       <c r="A2" s="2" t="s">
@@ -1923,7 +2083,7 @@
       <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="K2" s="30" t="s">
         <v>11</v>
       </c>
       <c r="L2" s="3" t="s">
@@ -1936,36 +2096,36 @@
         <v>14</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="51" customHeight="1" thickBot="1">
       <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="51" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="54" t="s">
+      <c r="F3" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="52" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I3" s="21"/>
-      <c r="J3" s="53" t="s">
+      <c r="J3" s="52" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="21">
@@ -1979,34 +2139,34 @@
         <v>1600</v>
       </c>
       <c r="N3" s="21"/>
-      <c r="O3" s="85"/>
+      <c r="O3" s="77"/>
     </row>
     <row r="4" spans="1:30" ht="51" customHeight="1" thickBot="1">
       <c r="A4" s="5">
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="55" t="s">
+      <c r="B4" s="87"/>
+      <c r="C4" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="56" t="s">
+      <c r="D4" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="56" t="s">
+      <c r="E4" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="57" t="s">
+      <c r="F4" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="56" t="s">
+      <c r="G4" s="55" t="s">
         <v>27</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>28</v>
       </c>
       <c r="I4" s="14"/>
-      <c r="J4" s="56" t="s">
+      <c r="J4" s="55" t="s">
         <v>29</v>
       </c>
       <c r="K4" s="14">
@@ -2016,35 +2176,35 @@
         <v>1</v>
       </c>
       <c r="M4" s="14">
-        <f t="shared" ref="M4:M31" si="0">L4*400</f>
+        <f t="shared" ref="M4:M34" si="0">L4*400</f>
         <v>400</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="O4" s="85" t="s">
-        <v>208</v>
+      <c r="O4" s="77" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="51" customHeight="1" thickBot="1">
       <c r="A5" s="5">
-        <f t="shared" ref="A5:A31" si="1">A4+1</f>
+        <f t="shared" ref="A5:A34" si="1">A4+1</f>
         <v>3</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="55" t="s">
+      <c r="B5" s="87"/>
+      <c r="C5" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="56" t="s">
+      <c r="D5" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="56" t="s">
+      <c r="E5" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="56" t="s">
+      <c r="G5" s="55" t="s">
         <v>34</v>
       </c>
       <c r="H5" s="13" t="s">
@@ -2053,7 +2213,7 @@
       <c r="I5" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="56" t="s">
+      <c r="J5" s="55" t="s">
         <v>37</v>
       </c>
       <c r="K5" s="14">
@@ -2067,36 +2227,36 @@
         <v>3200</v>
       </c>
       <c r="N5" s="14"/>
-      <c r="O5" s="85"/>
+      <c r="O5" s="77"/>
     </row>
     <row r="6" spans="1:30" ht="51" customHeight="1" thickBot="1">
       <c r="A6" s="5">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="58" t="s">
+      <c r="B6" s="87"/>
+      <c r="C6" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="F6" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="60" t="s">
+      <c r="G6" s="59" t="s">
         <v>41</v>
       </c>
       <c r="H6" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="61" t="s">
+      <c r="I6" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="59" t="s">
+      <c r="J6" s="58" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="14">
@@ -2109,11 +2269,11 @@
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="N6" s="34" t="s">
+      <c r="N6" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="89" t="s">
-        <v>209</v>
+      <c r="O6" s="81" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="51" customHeight="1" thickBot="1">
@@ -2121,20 +2281,20 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="58" t="s">
+      <c r="B7" s="87"/>
+      <c r="C7" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="57" t="s">
+      <c r="F7" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="60" t="s">
+      <c r="G7" s="59" t="s">
         <v>49</v>
       </c>
       <c r="H7" s="16" t="s">
@@ -2143,7 +2303,7 @@
       <c r="I7" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="59" t="s">
+      <c r="J7" s="58" t="s">
         <v>52</v>
       </c>
       <c r="K7" s="14">
@@ -2157,53 +2317,53 @@
         <v>400</v>
       </c>
       <c r="N7" s="14"/>
-      <c r="O7" s="85"/>
-    </row>
-    <row r="8" spans="1:30" ht="72.599999999999994" thickBot="1">
+      <c r="O7" s="77"/>
+    </row>
+    <row r="8" spans="1:30" ht="75.75" thickBot="1">
       <c r="A8" s="5">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B8" s="83"/>
-      <c r="C8" s="58" t="s">
+      <c r="B8" s="87"/>
+      <c r="C8" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="59" t="s">
+      <c r="E8" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="57" t="s">
+      <c r="F8" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="60" t="s">
+      <c r="G8" s="59" t="s">
         <v>57</v>
       </c>
       <c r="H8" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="62" t="s">
+      <c r="I8" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="J8" s="59" t="s">
+      <c r="J8" s="58" t="s">
         <v>60</v>
       </c>
       <c r="K8" s="14">
         <v>420</v>
       </c>
-      <c r="L8" s="35">
+      <c r="L8" s="34">
         <v>1</v>
       </c>
       <c r="M8" s="14">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N8" s="36" t="s">
+      <c r="N8" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="O8" s="89" t="s">
-        <v>211</v>
+      <c r="O8" s="81" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="51" customHeight="1" thickBot="1">
@@ -2211,72 +2371,72 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B9" s="83"/>
-      <c r="C9" s="58" t="s">
+      <c r="B9" s="87"/>
+      <c r="C9" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="59" t="s">
+      <c r="E9" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="57" t="s">
+      <c r="F9" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="60" t="s">
+      <c r="G9" s="59" t="s">
         <v>57</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="62" t="s">
+      <c r="I9" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="59" t="s">
+      <c r="J9" s="58" t="s">
         <v>60</v>
       </c>
       <c r="K9" s="14">
         <v>850</v>
       </c>
-      <c r="L9" s="35">
+      <c r="L9" s="34">
         <v>2</v>
       </c>
       <c r="M9" s="14">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="N9" s="37"/>
-      <c r="O9" s="85"/>
-    </row>
-    <row r="10" spans="1:30" ht="72.599999999999994" thickBot="1">
+      <c r="N9" s="36"/>
+      <c r="O9" s="77"/>
+    </row>
+    <row r="10" spans="1:30" ht="90.75" thickBot="1">
       <c r="A10" s="5">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B10" s="83"/>
-      <c r="C10" s="58" t="s">
+      <c r="B10" s="87"/>
+      <c r="C10" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="59" t="s">
+      <c r="E10" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="57" t="s">
+      <c r="F10" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="60" t="s">
+      <c r="G10" s="59" t="s">
         <v>69</v>
       </c>
       <c r="H10" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="62" t="s">
+      <c r="I10" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="J10" s="59" t="s">
+      <c r="J10" s="58" t="s">
         <v>71</v>
       </c>
       <c r="K10" s="14">
@@ -2289,42 +2449,39 @@
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N10" s="38" t="s">
+      <c r="N10" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="O10" s="89" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" ht="51" customHeight="1" thickBot="1">
+      <c r="O10" s="81" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="15.75" thickBot="1">
       <c r="A11" s="5">
-        <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="B11" s="83"/>
-      <c r="C11" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="59" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="57" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="I11" s="62" t="s">
+      <c r="B11" s="87"/>
+      <c r="C11" s="91" t="s">
+        <v>215</v>
+      </c>
+      <c r="D11" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="93" t="s">
+        <v>213</v>
+      </c>
+      <c r="G11" s="93" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="95" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="59" t="s">
-        <v>79</v>
+      <c r="I11" s="61"/>
+      <c r="J11" s="58" t="s">
+        <v>71</v>
       </c>
       <c r="K11" s="14">
         <v>420</v>
@@ -2336,58 +2493,53 @@
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N11" s="90" t="s">
-        <v>80</v>
-      </c>
-      <c r="O11" s="91" t="s">
-        <v>208</v>
-      </c>
+      <c r="N11" s="37"/>
+      <c r="O11" s="81"/>
     </row>
     <row r="12" spans="1:30" ht="51" customHeight="1" thickBot="1">
       <c r="A12" s="5">
-        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B12" s="84"/>
-      <c r="C12" s="63" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="64" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="65" t="s">
-        <v>84</v>
-      </c>
-      <c r="G12" s="66" t="s">
-        <v>85</v>
-      </c>
-      <c r="H12" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="I12" s="67" t="s">
+      <c r="B12" s="87"/>
+      <c r="C12" s="91" t="s">
+        <v>214</v>
+      </c>
+      <c r="D12" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="92" t="s">
+        <v>217</v>
+      </c>
+      <c r="G12" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="I12" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="J12" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="K12" s="17">
-        <v>450</v>
-      </c>
-      <c r="L12" s="19">
+      <c r="J12" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="14">
+        <v>420</v>
+      </c>
+      <c r="L12" s="15">
         <v>1</v>
       </c>
-      <c r="M12" s="17">
+      <c r="M12" s="14">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N12" s="92" t="s">
-        <v>88</v>
-      </c>
-      <c r="O12" s="91" t="s">
-        <v>208</v>
+      <c r="N12" s="82" t="s">
+        <v>75</v>
+      </c>
+      <c r="O12" s="83" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="51" customHeight="1" thickBot="1">
@@ -2395,899 +2547,1028 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="B13" s="82" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="68" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="69" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="G13" s="69" t="s">
-        <v>94</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="I13" s="70" t="s">
+      <c r="B13" s="90"/>
+      <c r="C13" s="62" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="63" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="64" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="65" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="J13" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="21">
-        <v>420</v>
-      </c>
-      <c r="L13" s="39">
+      <c r="J13" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" s="17">
+        <v>450</v>
+      </c>
+      <c r="L13" s="19">
         <v>1</v>
       </c>
-      <c r="M13" s="21">
+      <c r="M13" s="17">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N13" s="21"/>
-      <c r="O13" s="87"/>
+      <c r="N13" s="84" t="s">
+        <v>83</v>
+      </c>
+      <c r="O13" s="83" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="14" spans="1:30" ht="51" customHeight="1" thickBot="1">
       <c r="A14" s="5">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B14" s="84"/>
-      <c r="C14" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" s="64" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" s="64" t="s">
-        <v>99</v>
-      </c>
-      <c r="F14" s="65" t="s">
-        <v>100</v>
-      </c>
-      <c r="G14" s="64" t="s">
-        <v>101</v>
-      </c>
-      <c r="H14" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="I14" s="67" t="s">
+      <c r="B14" s="86" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="66" t="s">
-        <v>96</v>
-      </c>
-      <c r="K14" s="17">
+      <c r="J14" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="21">
         <v>420</v>
       </c>
-      <c r="L14" s="40">
+      <c r="L14" s="38">
         <v>1</v>
       </c>
-      <c r="M14" s="17">
+      <c r="M14" s="21">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N14" s="41"/>
-      <c r="O14" s="86"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="79"/>
     </row>
     <row r="15" spans="1:30" ht="51" customHeight="1" thickBot="1">
       <c r="A15" s="5">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="72" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" s="73" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" s="73" t="s">
-        <v>106</v>
-      </c>
-      <c r="F15" s="73" t="s">
-        <v>107</v>
-      </c>
-      <c r="G15" s="74" t="s">
-        <v>108</v>
-      </c>
-      <c r="H15" s="74" t="s">
+      <c r="B15" s="90"/>
+      <c r="C15" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="66" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="73" t="s">
-        <v>59</v>
-      </c>
-      <c r="J15" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="K15" s="25">
+      <c r="J15" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" s="17">
         <v>420</v>
       </c>
-      <c r="L15" s="25">
+      <c r="L15" s="39">
         <v>1</v>
       </c>
-      <c r="M15" s="24">
+      <c r="M15" s="17">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N15" s="42"/>
-      <c r="O15" s="88"/>
-    </row>
-    <row r="16" spans="1:30" ht="82.05" customHeight="1" thickBot="1">
+      <c r="N15" s="40"/>
+      <c r="O15" s="78"/>
+    </row>
+    <row r="16" spans="1:30" ht="51" customHeight="1" thickBot="1">
       <c r="A16" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" s="75" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="76" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" s="76" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="76" t="s">
-        <v>112</v>
-      </c>
-      <c r="G16" s="76" t="s">
-        <v>113</v>
-      </c>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="76" t="s">
-        <v>96</v>
-      </c>
-      <c r="K16" s="26">
+        <v>98</v>
+      </c>
+      <c r="C16" s="71" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="72" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="72" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="72" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" s="73" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="72" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="K16" s="25">
         <v>420</v>
       </c>
-      <c r="L16" s="26">
+      <c r="L16" s="25">
         <v>1</v>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="24">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N16" s="93" t="s">
-        <v>114</v>
-      </c>
-      <c r="O16" s="94" t="s">
-        <v>210</v>
-      </c>
+      <c r="N16" s="41"/>
+      <c r="O16" s="80"/>
     </row>
     <row r="17" spans="1:15" ht="51" customHeight="1" thickBot="1">
       <c r="A17" s="5">
-        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="86" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="115" t="s">
+        <v>219</v>
+      </c>
+      <c r="D17" s="99" t="s">
+        <v>220</v>
+      </c>
+      <c r="E17" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="93" t="s">
+        <v>221</v>
+      </c>
+      <c r="G17" s="112" t="s">
+        <v>228</v>
+      </c>
+      <c r="H17" s="114" t="s">
+        <v>229</v>
+      </c>
+      <c r="I17" s="101"/>
+      <c r="J17" s="94" t="s">
+        <v>230</v>
+      </c>
+      <c r="K17" s="102">
+        <v>420</v>
+      </c>
+      <c r="L17" s="102">
+        <v>1</v>
+      </c>
+      <c r="M17" s="103">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="N17" s="104"/>
+      <c r="O17" s="105"/>
+    </row>
+    <row r="18" spans="1:15" ht="82.15" customHeight="1" thickBot="1">
+      <c r="A18" s="5">
         <v>15</v>
       </c>
-      <c r="B17" s="82" t="s">
+      <c r="B18" s="90"/>
+      <c r="C18" s="106" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="107" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="107" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="107" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" s="107" t="s">
+        <v>108</v>
+      </c>
+      <c r="H18" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="108"/>
+      <c r="J18" s="116" t="s">
+        <v>231</v>
+      </c>
+      <c r="K18" s="108">
+        <v>420</v>
+      </c>
+      <c r="L18" s="108">
+        <v>1</v>
+      </c>
+      <c r="M18" s="108">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="N18" s="109" t="s">
+        <v>109</v>
+      </c>
+      <c r="O18" s="110" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="51" customHeight="1" thickBot="1">
+      <c r="A19" s="5">
+        <f>A18+1</f>
+        <v>16</v>
+      </c>
+      <c r="B19" s="86" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="74" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" s="69" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="77" t="s">
+      <c r="I19" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="J19" s="53" t="s">
         <v>116</v>
       </c>
-      <c r="D17" s="54" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" s="54" t="s">
-        <v>119</v>
-      </c>
-      <c r="G17" s="70" t="s">
-        <v>85</v>
-      </c>
-      <c r="H17" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="I17" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="J17" s="54" t="s">
-        <v>121</v>
-      </c>
-      <c r="K17" s="8">
+      <c r="K19" s="8">
         <v>900</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L19" s="8">
         <v>2</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M19" s="8">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="N17" s="43" t="s">
+      <c r="N19" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="O19" s="79" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="51" customHeight="1" thickBot="1">
+      <c r="A20" s="5">
+        <v>17</v>
+      </c>
+      <c r="B20" s="87"/>
+      <c r="C20" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="E20" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" s="92" t="s">
+        <v>223</v>
+      </c>
+      <c r="G20" s="92" t="s">
+        <v>198</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="I20" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" s="98" t="s">
+        <v>226</v>
+      </c>
+      <c r="K20" s="96">
+        <v>900</v>
+      </c>
+      <c r="L20" s="96">
+        <v>1</v>
+      </c>
+      <c r="M20" s="96"/>
+      <c r="N20" s="97"/>
+      <c r="O20" s="79"/>
+    </row>
+    <row r="21" spans="1:15" ht="51" customHeight="1" thickBot="1">
+      <c r="A21" s="5">
+        <v>18</v>
+      </c>
+      <c r="B21" s="87"/>
+      <c r="C21" s="75" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="I21" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="O17" s="87" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="51" customHeight="1" thickBot="1">
-      <c r="A18" s="5">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="B18" s="83"/>
-      <c r="C18" s="78" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="F18" s="57" t="s">
-        <v>125</v>
-      </c>
-      <c r="G18" s="62" t="s">
-        <v>85</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I18" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="J18" s="57" t="s">
-        <v>127</v>
-      </c>
-      <c r="K18" s="11">
+      <c r="K21" s="11">
         <v>900</v>
       </c>
-      <c r="L18" s="11">
+      <c r="L21" s="11">
         <v>2</v>
       </c>
-      <c r="M18" s="11">
+      <c r="M21" s="11">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="N18" s="11"/>
-      <c r="O18" s="85"/>
-    </row>
-    <row r="19" spans="1:15" ht="51" customHeight="1" thickBot="1">
-      <c r="A19" s="5">
+      <c r="N21" s="11"/>
+      <c r="O21" s="77"/>
+    </row>
+    <row r="22" spans="1:15" ht="51" customHeight="1" thickBot="1">
+      <c r="A22" s="5">
         <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="B19" s="83"/>
-      <c r="C19" s="78" t="s">
-        <v>128</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="G19" s="62" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="I19" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="87"/>
+      <c r="C22" s="75" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E22" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="F22" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="J19" s="57" t="s">
-        <v>132</v>
-      </c>
-      <c r="K19" s="11">
+      <c r="J22" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="K22" s="11">
         <v>1300</v>
       </c>
-      <c r="L19" s="11">
+      <c r="L22" s="11">
         <v>3</v>
       </c>
-      <c r="M19" s="11">
+      <c r="M22" s="11">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="N19" s="11"/>
-      <c r="O19" s="85"/>
-    </row>
-    <row r="20" spans="1:15" ht="51" customHeight="1" thickBot="1">
-      <c r="A20" s="5">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="B20" s="83"/>
-      <c r="C20" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="57" t="s">
-        <v>134</v>
-      </c>
-      <c r="E20" s="57" t="s">
-        <v>135</v>
-      </c>
-      <c r="F20" s="57" t="s">
-        <v>136</v>
-      </c>
-      <c r="G20" s="62" t="s">
-        <v>137</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="I20" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="J20" s="57" t="s">
-        <v>139</v>
-      </c>
-      <c r="K20" s="11">
-        <v>820</v>
-      </c>
-      <c r="L20" s="11">
-        <v>2</v>
-      </c>
-      <c r="M20" s="11">
-        <f t="shared" si="0"/>
-        <v>800</v>
-      </c>
-      <c r="N20" s="11"/>
-      <c r="O20" s="85"/>
-    </row>
-    <row r="21" spans="1:15" ht="51" customHeight="1" thickBot="1">
-      <c r="A21" s="5">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="B21" s="83"/>
-      <c r="C21" s="78" t="s">
-        <v>140</v>
-      </c>
-      <c r="D21" s="57" t="s">
-        <v>141</v>
-      </c>
-      <c r="E21" s="57" t="s">
-        <v>135</v>
-      </c>
-      <c r="F21" s="57" t="s">
-        <v>142</v>
-      </c>
-      <c r="G21" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="I21" s="62" t="s">
-        <v>145</v>
-      </c>
-      <c r="J21" s="57" t="s">
-        <v>146</v>
-      </c>
-      <c r="K21" s="11">
-        <v>420</v>
-      </c>
-      <c r="L21" s="11">
-        <v>1</v>
-      </c>
-      <c r="M21" s="11">
-        <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="N21" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="O21" s="85" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="58.05" customHeight="1" thickBot="1">
-      <c r="A22" s="5">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="B22" s="83"/>
-      <c r="C22" s="78" t="s">
-        <v>148</v>
-      </c>
-      <c r="D22" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="E22" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="G22" s="62" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="I22" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="J22" s="57" t="s">
-        <v>153</v>
-      </c>
-      <c r="K22" s="11">
-        <v>500</v>
-      </c>
-      <c r="L22" s="11">
-        <v>1</v>
-      </c>
-      <c r="M22" s="11">
-        <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="N22" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="O22" s="89" t="s">
-        <v>213</v>
-      </c>
+      <c r="N22" s="11"/>
+      <c r="O22" s="77"/>
     </row>
     <row r="23" spans="1:15" ht="51" customHeight="1" thickBot="1">
       <c r="A23" s="5">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="B23" s="84"/>
-      <c r="C23" s="79" t="s">
-        <v>155</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="E23" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="F23" s="65" t="s">
-        <v>157</v>
-      </c>
-      <c r="G23" s="67" t="s">
-        <v>85</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="I23" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="87"/>
+      <c r="C23" s="75" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="I23" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="J23" s="65" t="s">
-        <v>159</v>
-      </c>
-      <c r="K23" s="18">
-        <v>3300</v>
-      </c>
-      <c r="L23" s="20">
-        <v>8</v>
-      </c>
-      <c r="M23" s="18">
+      <c r="J23" s="56" t="s">
+        <v>134</v>
+      </c>
+      <c r="K23" s="11">
+        <v>820</v>
+      </c>
+      <c r="L23" s="11">
+        <v>2</v>
+      </c>
+      <c r="M23" s="11">
         <f t="shared" si="0"/>
-        <v>3200</v>
-      </c>
-      <c r="N23" s="18"/>
-      <c r="O23" s="86"/>
+        <v>800</v>
+      </c>
+      <c r="N23" s="11"/>
+      <c r="O23" s="77"/>
     </row>
     <row r="24" spans="1:15" ht="51" customHeight="1" thickBot="1">
       <c r="A24" s="5">
         <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="B24" s="82" t="s">
-        <v>160</v>
-      </c>
-      <c r="C24" s="77" t="s">
-        <v>161</v>
-      </c>
-      <c r="D24" s="54" t="s">
-        <v>162</v>
-      </c>
-      <c r="E24" s="54" t="s">
-        <v>163</v>
-      </c>
-      <c r="F24" s="54" t="s">
-        <v>164</v>
-      </c>
-      <c r="G24" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="H24" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="I24" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="J24" s="70" t="s">
-        <v>96</v>
-      </c>
-      <c r="K24" s="22">
+        <v>21</v>
+      </c>
+      <c r="B24" s="87"/>
+      <c r="C24" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="E24" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="I24" s="61" t="s">
+        <v>140</v>
+      </c>
+      <c r="J24" s="56" t="s">
+        <v>141</v>
+      </c>
+      <c r="K24" s="11">
         <v>420</v>
       </c>
-      <c r="L24" s="22">
+      <c r="L24" s="11">
         <v>1</v>
       </c>
-      <c r="M24" s="8">
+      <c r="M24" s="11">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N24" s="8"/>
-      <c r="O24" s="87"/>
-    </row>
-    <row r="25" spans="1:15" ht="51" customHeight="1" thickBot="1">
+      <c r="N24" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="O24" s="77" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="58.15" customHeight="1" thickBot="1">
       <c r="A25" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="B25" s="83"/>
-      <c r="C25" s="78" t="s">
-        <v>166</v>
-      </c>
-      <c r="D25" s="57" t="s">
-        <v>167</v>
-      </c>
-      <c r="E25" s="57" t="s">
-        <v>168</v>
-      </c>
-      <c r="F25" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="G25" s="62" t="s">
-        <v>170</v>
+        <v>22</v>
+      </c>
+      <c r="B25" s="87"/>
+      <c r="C25" s="75" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" s="56" t="s">
+        <v>144</v>
+      </c>
+      <c r="E25" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="G25" s="61" t="s">
+        <v>146</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="I25" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="I25" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="J25" s="62" t="s">
-        <v>96</v>
-      </c>
-      <c r="K25" s="16">
-        <v>420</v>
-      </c>
-      <c r="L25" s="16">
+      <c r="J25" s="56" t="s">
+        <v>148</v>
+      </c>
+      <c r="K25" s="11">
+        <v>500</v>
+      </c>
+      <c r="L25" s="11">
         <v>1</v>
       </c>
       <c r="M25" s="11">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N25" s="11"/>
-      <c r="O25" s="85"/>
+      <c r="N25" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="O25" s="81" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="26" spans="1:15" ht="51" customHeight="1" thickBot="1">
       <c r="A26" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="B26" s="84"/>
-      <c r="C26" s="79" t="s">
-        <v>172</v>
-      </c>
-      <c r="D26" s="65" t="s">
-        <v>173</v>
-      </c>
-      <c r="E26" s="65" t="s">
-        <v>174</v>
-      </c>
-      <c r="F26" s="65" t="s">
-        <v>175</v>
-      </c>
-      <c r="G26" s="67" t="s">
-        <v>176</v>
+        <v>23</v>
+      </c>
+      <c r="B26" s="90"/>
+      <c r="C26" s="76" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="64" t="s">
+        <v>152</v>
+      </c>
+      <c r="G26" s="66" t="s">
+        <v>80</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="I26" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="I26" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20">
-        <v>420</v>
+      <c r="J26" s="64" t="s">
+        <v>154</v>
+      </c>
+      <c r="K26" s="18">
+        <v>3300</v>
       </c>
       <c r="L26" s="20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M26" s="18">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="N26" s="41"/>
-      <c r="O26" s="86"/>
+        <v>3200</v>
+      </c>
+      <c r="N26" s="18"/>
+      <c r="O26" s="78"/>
     </row>
     <row r="27" spans="1:15" ht="51" customHeight="1" thickBot="1">
       <c r="A27" s="5">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="B27" s="82" t="s">
-        <v>178</v>
-      </c>
-      <c r="C27" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="D27" s="54" t="s">
-        <v>180</v>
-      </c>
-      <c r="E27" s="54" t="s">
-        <v>181</v>
-      </c>
-      <c r="F27" s="54" t="s">
-        <v>181</v>
-      </c>
-      <c r="G27" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8">
+        <v>24</v>
+      </c>
+      <c r="B27" s="86" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="74" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>158</v>
+      </c>
+      <c r="F27" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="G27" s="69" t="s">
+        <v>160</v>
+      </c>
+      <c r="H27" s="69" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="J27" s="69" t="s">
+        <v>91</v>
+      </c>
+      <c r="K27" s="22">
         <v>420</v>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="22">
         <v>1</v>
       </c>
       <c r="M27" s="8">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N27" s="46" t="s">
-        <v>183</v>
-      </c>
-      <c r="O27" s="95" t="s">
-        <v>215</v>
-      </c>
+      <c r="N27" s="8"/>
+      <c r="O27" s="79"/>
     </row>
     <row r="28" spans="1:15" ht="51" customHeight="1" thickBot="1">
       <c r="A28" s="5">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="B28" s="83"/>
-      <c r="C28" s="78" t="s">
-        <v>184</v>
-      </c>
-      <c r="D28" s="57" t="s">
-        <v>185</v>
-      </c>
-      <c r="E28" s="57" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="G28" s="57" t="s">
-        <v>187</v>
-      </c>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="16"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="87"/>
+      <c r="C28" s="75" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="E28" s="56" t="s">
+        <v>163</v>
+      </c>
+      <c r="F28" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="G28" s="61" t="s">
+        <v>165</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="I28" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="J28" s="61" t="s">
+        <v>91</v>
+      </c>
       <c r="K28" s="16">
-        <v>820</v>
-      </c>
-      <c r="L28" s="11">
-        <v>2</v>
+        <v>420</v>
+      </c>
+      <c r="L28" s="16">
+        <v>1</v>
       </c>
       <c r="M28" s="11">
         <f t="shared" si="0"/>
-        <v>800</v>
-      </c>
-      <c r="N28" s="47"/>
-      <c r="O28" s="85"/>
+        <v>400</v>
+      </c>
+      <c r="N28" s="11"/>
+      <c r="O28" s="77"/>
     </row>
     <row r="29" spans="1:15" ht="51" customHeight="1" thickBot="1">
       <c r="A29" s="5">
         <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="B29" s="83"/>
-      <c r="C29" s="78" t="s">
-        <v>188</v>
-      </c>
-      <c r="D29" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="E29" s="57" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="57" t="s">
-        <v>190</v>
-      </c>
-      <c r="G29" s="57" t="s">
-        <v>182</v>
-      </c>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16">
+        <v>26</v>
+      </c>
+      <c r="B29" s="90"/>
+      <c r="C29" s="76" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" s="64" t="s">
+        <v>168</v>
+      </c>
+      <c r="E29" s="64" t="s">
+        <v>169</v>
+      </c>
+      <c r="F29" s="64" t="s">
+        <v>170</v>
+      </c>
+      <c r="G29" s="66" t="s">
+        <v>171</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="I29" s="64" t="s">
+        <v>59</v>
+      </c>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20">
         <v>420</v>
       </c>
-      <c r="L29" s="11">
+      <c r="L29" s="20">
         <v>1</v>
       </c>
-      <c r="M29" s="11">
+      <c r="M29" s="18">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N29" s="48" t="s">
-        <v>191</v>
-      </c>
-      <c r="O29" s="89" t="s">
-        <v>214</v>
-      </c>
+      <c r="N29" s="40"/>
+      <c r="O29" s="78"/>
     </row>
     <row r="30" spans="1:15" ht="51" customHeight="1" thickBot="1">
       <c r="A30" s="5">
         <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="B30" s="83"/>
-      <c r="C30" s="78" t="s">
-        <v>192</v>
-      </c>
-      <c r="D30" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="E30" s="57" t="s">
-        <v>194</v>
-      </c>
-      <c r="F30" s="57" t="s">
-        <v>195</v>
-      </c>
-      <c r="G30" s="57" t="s">
-        <v>196</v>
-      </c>
-      <c r="H30" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="I30" s="11"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16">
+        <v>27</v>
+      </c>
+      <c r="B30" s="86" t="s">
+        <v>173</v>
+      </c>
+      <c r="C30" s="74" t="s">
+        <v>174</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="G30" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8">
         <v>420</v>
       </c>
-      <c r="L30" s="11">
+      <c r="L30" s="8">
         <v>1</v>
       </c>
-      <c r="M30" s="11">
+      <c r="M30" s="8">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="N30" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="O30" s="89" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="51" customHeight="1">
+      <c r="N30" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="O30" s="85" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="51" customHeight="1" thickBot="1">
       <c r="A31" s="5">
         <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="B31" s="83"/>
-      <c r="C31" s="78" t="s">
-        <v>199</v>
-      </c>
-      <c r="D31" s="57" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="F31" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="G31" s="57" t="s">
-        <v>203</v>
-      </c>
-      <c r="H31" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="I31" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="J31" s="62" t="s">
-        <v>96</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B31" s="87"/>
+      <c r="C31" s="75" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="G31" s="56" t="s">
+        <v>182</v>
+      </c>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="16"/>
       <c r="K31" s="16">
-        <v>850</v>
-      </c>
-      <c r="L31" s="16">
+        <v>820</v>
+      </c>
+      <c r="L31" s="11">
         <v>2</v>
       </c>
       <c r="M31" s="11">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="N31" s="45" t="s">
-        <v>205</v>
-      </c>
-      <c r="O31" s="85" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="51" customHeight="1">
-      <c r="A32"/>
-      <c r="O32" s="32"/>
-    </row>
-    <row r="33" spans="1:15" ht="51" customHeight="1">
-      <c r="A33"/>
-      <c r="O33" s="32"/>
-    </row>
-    <row r="34" spans="1:15" ht="51" customHeight="1">
-      <c r="A34"/>
-      <c r="O34" s="32"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="77"/>
+    </row>
+    <row r="32" spans="1:15" ht="51" customHeight="1" thickBot="1">
+      <c r="A32" s="5">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="87"/>
+      <c r="C32" s="75" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" s="56" t="s">
+        <v>184</v>
+      </c>
+      <c r="E32" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="F32" s="56" t="s">
+        <v>185</v>
+      </c>
+      <c r="G32" s="56" t="s">
+        <v>177</v>
+      </c>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16">
+        <v>420</v>
+      </c>
+      <c r="L32" s="11">
+        <v>1</v>
+      </c>
+      <c r="M32" s="11">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="N32" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="O32" s="81" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="51" customHeight="1" thickBot="1">
+      <c r="A33" s="5">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="87"/>
+      <c r="C33" s="75" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" s="56" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="G33" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="H33" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="I33" s="11"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16">
+        <v>420</v>
+      </c>
+      <c r="L33" s="11">
+        <v>1</v>
+      </c>
+      <c r="M33" s="11">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="N33" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="O33" s="81" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="51" customHeight="1" thickBot="1">
+      <c r="A34" s="5">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="90"/>
+      <c r="C34" s="75" t="s">
+        <v>194</v>
+      </c>
+      <c r="D34" s="56" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" s="56" t="s">
+        <v>196</v>
+      </c>
+      <c r="F34" s="56" t="s">
+        <v>197</v>
+      </c>
+      <c r="G34" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="I34" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="J34" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="K34" s="16">
+        <v>850</v>
+      </c>
+      <c r="L34" s="16">
+        <v>2</v>
+      </c>
+      <c r="M34" s="11">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="N34" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="O34" s="77" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="35" spans="1:15" ht="51" customHeight="1">
-      <c r="A35"/>
-      <c r="O35" s="32"/>
+      <c r="A35" s="111" t="s">
+        <v>227</v>
+      </c>
+      <c r="O35" s="31"/>
     </row>
     <row r="36" spans="1:15" ht="51" customHeight="1">
       <c r="A36"/>
-      <c r="E36" t="s">
-        <v>206</v>
-      </c>
-      <c r="O36" s="32"/>
+      <c r="O36" s="31"/>
     </row>
     <row r="37" spans="1:15" ht="51" customHeight="1">
       <c r="A37"/>
-      <c r="O37" s="32"/>
+      <c r="O37" s="31"/>
     </row>
     <row r="38" spans="1:15" ht="51" customHeight="1">
       <c r="A38"/>
-      <c r="O38" s="32"/>
+      <c r="O38" s="31"/>
     </row>
     <row r="39" spans="1:15" ht="51" customHeight="1">
       <c r="A39"/>
-      <c r="O39" s="32"/>
+      <c r="E39" t="s">
+        <v>201</v>
+      </c>
+      <c r="O39" s="31"/>
     </row>
     <row r="40" spans="1:15" ht="51" customHeight="1">
       <c r="A40"/>
-      <c r="O40" s="32"/>
+      <c r="O40" s="31"/>
     </row>
     <row r="41" spans="1:15" ht="51" customHeight="1">
       <c r="A41"/>
-      <c r="O41" s="32"/>
+      <c r="O41" s="31"/>
     </row>
     <row r="42" spans="1:15" ht="51" customHeight="1">
       <c r="A42"/>
-      <c r="O42" s="32"/>
+      <c r="O42" s="31"/>
     </row>
     <row r="43" spans="1:15" ht="51" customHeight="1">
-      <c r="H43" s="29"/>
-      <c r="N43" s="50"/>
+      <c r="A43"/>
+      <c r="O43" s="31"/>
     </row>
     <row r="44" spans="1:15" ht="51" customHeight="1">
-      <c r="H44" s="29"/>
-      <c r="N44" s="50"/>
+      <c r="A44"/>
+      <c r="O44" s="31"/>
+    </row>
+    <row r="45" spans="1:15" ht="51" customHeight="1">
+      <c r="A45"/>
+      <c r="O45" s="31"/>
+    </row>
+    <row r="46" spans="1:15" ht="51" customHeight="1">
+      <c r="H46" s="28"/>
+      <c r="N46" s="49"/>
+    </row>
+    <row r="47" spans="1:15" ht="51" customHeight="1">
+      <c r="H47" s="28"/>
+      <c r="N47" s="49"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B27:B31"/>
+  <mergeCells count="7">
+    <mergeCell ref="B30:B34"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="B3:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B3:B13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B19:B26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B17:B18"/>
   </mergeCells>
-  <conditionalFormatting sqref="N11">
+  <conditionalFormatting sqref="N12">
     <cfRule type="dataBar" priority="40">
       <dataBar>
         <cfvo type="min"/>
@@ -3301,7 +3582,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N15">
+  <conditionalFormatting sqref="N16:N17">
     <cfRule type="dataBar" priority="41">
       <dataBar>
         <cfvo type="min"/>
@@ -3315,7 +3596,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L27:M27">
+  <conditionalFormatting sqref="L30:M30">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -3327,7 +3608,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L6:L10">
+  <conditionalFormatting sqref="L6:L11">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
@@ -3339,7 +3620,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N27:N30">
+  <conditionalFormatting sqref="N30:N33">
     <cfRule type="dataBar" priority="42">
       <dataBar>
         <cfvo type="min"/>
@@ -3353,7 +3634,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:M26 M28:M31 L11:L26 L31">
+  <conditionalFormatting sqref="M3:M29 M31:M34 L12:L29 L34">
     <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
@@ -3365,7 +3646,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:M31">
+  <conditionalFormatting sqref="L3:M34">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3393,7 +3674,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N11</xm:sqref>
+          <xm:sqref>N12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{56371448-1918-4725-BF8D-BAE246CFFAEE}">
@@ -3406,7 +3687,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N15</xm:sqref>
+          <xm:sqref>N16:N17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{9AECB0F9-E7EB-4A3B-87F7-4BFA9930A33F}">
@@ -3419,7 +3700,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N27:N30</xm:sqref>
+          <xm:sqref>N30:N33</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
